--- a/Heart Disease/Grouped Stats.xlsx
+++ b/Heart Disease/Grouped Stats.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10245" windowHeight="7170"/>
+    <workbookView windowWidth="20490" windowHeight="7620" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,24 @@
     <t>Age Groups</t>
   </si>
   <si>
+    <t>Average Cholesterol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg Chest Pain </t>
+  </si>
+  <si>
+    <t>Avg Max Heart Rate</t>
+  </si>
+  <si>
+    <t>Avg Bps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excercise Agnia Per </t>
+  </si>
+  <si>
+    <t>Heart Disease Per</t>
+  </si>
+  <si>
     <t>20-30</t>
   </si>
   <si>
@@ -48,37 +66,19 @@
     <t>61-Up</t>
   </si>
   <si>
-    <t>Average Cholesterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg Chest Pain </t>
-  </si>
-  <si>
-    <t>Avg Max Heart Rate</t>
-  </si>
-  <si>
-    <t>Avg Bps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excercise Agnia Per </t>
-  </si>
-  <si>
-    <t>Heart Disease Per</t>
-  </si>
-  <si>
     <t>Gender</t>
   </si>
   <si>
+    <t>Average Age</t>
+  </si>
+  <si>
+    <t>Age Variation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Male </t>
   </si>
   <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Average Age</t>
-  </si>
-  <si>
-    <t>Age Variation</t>
+    <t xml:space="preserve">Female </t>
   </si>
 </sst>
 </file>
@@ -1241,13 +1241,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="24.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="20.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="19.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="8.42857142857143" customWidth="1"/>
+    <col min="6" max="6" width="20.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1266,126 +1272,127 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>213.83</v>
       </c>
       <c r="C2">
+        <v>1.83</v>
+      </c>
+      <c r="D2">
+        <v>181.5</v>
+      </c>
+      <c r="E2">
+        <v>136.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
         <v>234.91</v>
-      </c>
-      <c r="D2">
-        <v>238.79</v>
-      </c>
-      <c r="E2">
-        <v>247.43</v>
-      </c>
-      <c r="F2">
-        <v>253.24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>1.83</v>
       </c>
       <c r="C3">
         <v>2.76</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
+        <v>158.5</v>
+      </c>
+      <c r="E3">
+        <v>125.3</v>
+      </c>
+      <c r="F3">
+        <v>20.4</v>
+      </c>
+      <c r="G3">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>238.79</v>
+      </c>
+      <c r="C4" s="3">
         <v>2.8</v>
-      </c>
-      <c r="E3">
-        <v>2.82</v>
-      </c>
-      <c r="F3">
-        <v>2.86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>181.5</v>
-      </c>
-      <c r="C4">
-        <v>158.5</v>
       </c>
       <c r="D4">
         <v>149.7</v>
       </c>
       <c r="E4">
+        <v>127.4</v>
+      </c>
+      <c r="F4">
+        <v>26.3</v>
+      </c>
+      <c r="G4">
+        <v>45.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>247.43</v>
+      </c>
+      <c r="C5">
+        <v>2.82</v>
+      </c>
+      <c r="D5">
         <v>140.5</v>
-      </c>
-      <c r="F4">
-        <v>132.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>136.6</v>
-      </c>
-      <c r="C5">
-        <v>125.3</v>
-      </c>
-      <c r="D5">
-        <v>127.4</v>
       </c>
       <c r="E5">
         <v>134.4</v>
       </c>
       <c r="F5">
+        <v>41.5</v>
+      </c>
+      <c r="G5">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>50.3</v>
+      </c>
+      <c r="C6">
+        <v>2.86</v>
+      </c>
+      <c r="D6">
+        <v>132.1</v>
+      </c>
+      <c r="E6">
         <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>20.4</v>
-      </c>
-      <c r="D6">
-        <v>26.3</v>
-      </c>
-      <c r="E6">
-        <v>41.5</v>
       </c>
       <c r="F6">
         <v>47.6</v>
       </c>
+      <c r="G6">
+        <v>59.8</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>16.6</v>
-      </c>
-      <c r="C7">
-        <v>34.4</v>
-      </c>
-      <c r="D7">
-        <v>45.4</v>
-      </c>
-      <c r="E7">
-        <v>50.3</v>
-      </c>
-      <c r="F7">
-        <v>59.8</v>
-      </c>
+    <row r="12" spans="3:3">
+      <c r="C12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1396,13 +1403,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="20.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="20.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="15.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="19.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="8.42857142857143" customWidth="1"/>
+    <col min="8" max="8" width="20.1428571428571" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1412,8 +1427,26 @@
       <c r="C1" t="s">
         <v>14</v>
       </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1421,86 +1454,64 @@
         <v>53.29</v>
       </c>
       <c r="C2">
-        <v>53.39</v>
+        <v>9.36</v>
+      </c>
+      <c r="D2">
+        <v>240.65</v>
+      </c>
+      <c r="E2">
+        <v>2.89</v>
+      </c>
+      <c r="F2">
+        <v>140.93</v>
+      </c>
+      <c r="G2">
+        <v>132.7</v>
+      </c>
+      <c r="H2">
+        <v>42.07</v>
+      </c>
+      <c r="I2">
+        <v>52.98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3">
-        <v>9.36</v>
+        <v>53.39</v>
       </c>
       <c r="C3">
         <v>9.49</v>
       </c>
+      <c r="D3">
+        <v>257.68</v>
+      </c>
+      <c r="E3">
+        <v>2.61</v>
+      </c>
+      <c r="F3">
+        <v>148.42</v>
+      </c>
+      <c r="G3">
+        <v>132.35</v>
+      </c>
+      <c r="H3">
+        <v>22.3</v>
+      </c>
+      <c r="I3">
+        <v>40.28</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>240.65</v>
-      </c>
-      <c r="C4">
-        <v>257.68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>2.89</v>
-      </c>
-      <c r="C5">
-        <v>2.61</v>
-      </c>
+    <row r="5" spans="4:4">
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>140.93</v>
-      </c>
-      <c r="C6">
-        <v>148.42</v>
-      </c>
+    <row r="7" spans="2:2">
+      <c r="B7" s="2"/>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2">
-        <v>132.7</v>
-      </c>
-      <c r="C7">
-        <v>132.35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>42.07</v>
-      </c>
-      <c r="C8" s="2">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>52.98</v>
-      </c>
-      <c r="C9">
-        <v>40.28</v>
-      </c>
+    <row r="8" spans="3:3">
+      <c r="C8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
